--- a/public/sap-reporting/expansion-150-downloads/EXT-FI28-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-FI28-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R7cbdc37221b14c6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R7ab02afc36164d7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R5d99648a337b4e8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Re995f48733cc463d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R47abe0abd5944305"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R394716c6fe3b4c79"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -521,7 +521,7 @@
         <x:v>0000100001</x:v>
       </x:c>
       <x:c r="N7" s="2" t="str">
-        <x:v>100.00</x:v>
+        <x:v>15.00</x:v>
       </x:c>
       <x:c r="O7" s="2" t="str">
         <x:v>0000100001</x:v>
@@ -854,7 +854,7 @@
         <x:v>0000100001</x:v>
       </x:c>
       <x:c r="N2" s="2" t="str">
-        <x:v>100.00</x:v>
+        <x:v>15.00</x:v>
       </x:c>
       <x:c r="O2" s="2" t="str">
         <x:v>0000100001</x:v>
